--- a/data/05_aviation.xlsx
+++ b/data/05_aviation.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R53e87f90c4904738"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aircraft" sheetId="2" r:id="R5208f856bdcb40f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aircraft Registry" sheetId="3" r:id="R4a0c37b9c6d74792"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aircraft Relationships" sheetId="4" r:id="R7ead685f8ebe4974"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aviation Fleet Summary" sheetId="5" r:id="R30e8dc621f774d27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carrier Deployment Seeds" sheetId="6" r:id="R0aaec8ee7ed54908"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rb24458ed5b584f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aircraft" sheetId="2" r:id="Rdf5c4f13007c41a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aircraft Registry" sheetId="3" r:id="R3894ff45a67048ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aircraft Relationships" sheetId="4" r:id="R2f05e5baa4b146f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aviation Fleet Summary" sheetId="5" r:id="Rd1a98c7708644991"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carrier Deployment Seeds" sheetId="6" r:id="Ra059bd31e1374c15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aviation Disruptions" sheetId="7" r:id="Rf293383836594a25"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -42,7 +43,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -59,6 +60,11 @@
         <x:fgColor rgb="FFC5A253"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -67,7 +73,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -90,6 +96,12 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -21579,4 +21591,205 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="38" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="42" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="42" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="48" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="36" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="19" t="str">
+        <x:v>Disruption ID</x:v>
+      </x:c>
+      <x:c r="B1" s="19" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="C1" s="19" t="str">
+        <x:v>Entity / Asset ID</x:v>
+      </x:c>
+      <x:c r="D1" s="19" t="str">
+        <x:v>Location</x:v>
+      </x:c>
+      <x:c r="E1" s="19" t="str">
+        <x:v>Country</x:v>
+      </x:c>
+      <x:c r="F1" s="19" t="str">
+        <x:v>Event Type</x:v>
+      </x:c>
+      <x:c r="G1" s="19" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="H1" s="19" t="str">
+        <x:v>Severity</x:v>
+      </x:c>
+      <x:c r="I1" s="19" t="str">
+        <x:v>Operational Impact</x:v>
+      </x:c>
+      <x:c r="J1" s="19" t="str">
+        <x:v>Trade / Cargo Impact</x:v>
+      </x:c>
+      <x:c r="K1" s="19" t="str">
+        <x:v>Cargo Exposure / Quantification</x:v>
+      </x:c>
+      <x:c r="L1" s="19" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="M1" s="19" t="str">
+        <x:v>Source URL</x:v>
+      </x:c>
+      <x:c r="N1" s="19" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="14" t="str">
+        <x:v>AVDIS_001</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str">
+        <x:v>COMP_NATS_UK</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="str">
+        <x:v>United Kingdom airspace</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="F2" s="14" t="str">
+        <x:v>Air traffic control technical failure</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="str">
+        <x:v>Recovery</x:v>
+      </x:c>
+      <x:c r="H2" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I2" s="14" t="str">
+        <x:v>Systemwide scheduling disruption; aircraft and crews displaced; ~1,300 flights cancelled.</x:v>
+      </x:c>
+      <x:c r="J2" s="14" t="str">
+        <x:v>Cargo capacity lost/delayed across UK gateways; missed connections and recovery backlogs; no cyberattack identified.</x:v>
+      </x:c>
+      <x:c r="K2" s="14" t="str">
+        <x:v>~1,300 flights cancelled (all traffic, not cargo-specific).</x:v>
+      </x:c>
+      <x:c r="L2" s="14" t="str">
+        <x:v>SRC_SEC_008</x:v>
+      </x:c>
+      <x:c r="M2" s="14" t="str">
+        <x:v>https://aircargoweek.com/nats-system-failure-leaves-uk-airlines-battling-a-second-day-of-disruption/</x:v>
+      </x:c>
+      <x:c r="N2" s="14" t="str">
+        <x:v>Classify as critical-infrastructure / operational disruption, not cyber.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="str">
+        <x:v>AVDIS_002</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="str">
+        <x:v>AIRPORT_JKIA</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>Jomo Kenyatta International Airport, Nairobi</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
+        <x:v>Kenya</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="str">
+        <x:v>Aviation labour strike</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="str">
+        <x:v>Recent / recurring</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="str">
+        <x:v>Cancellations, schedule changes and limited spare aircraft complicate recovery across regional routes.</x:v>
+      </x:c>
+      <x:c r="J3" s="14" t="str">
+        <x:v>Perishables and flower exports face high delay sensitivity; regional cargo connections to Rwanda, Burundi, Tanzania, Uganda, Somalia and Mauritius exposed.</x:v>
+      </x:c>
+      <x:c r="K3" s="14" t="str">
+        <x:v>5,500–7,000 tonnes weekly cargo; ACW estimated US$4m–6m of cargo value exposed by two disrupted days.</x:v>
+      </x:c>
+      <x:c r="L3" s="14" t="str">
+        <x:v>SRC_SEC_009</x:v>
+      </x:c>
+      <x:c r="M3" s="14" t="str">
+        <x:v>https://aircargoweek.com/kenya-aviation-strike-exposes-the-fragility-of-east-africas-air-cargo-gateway/</x:v>
+      </x:c>
+      <x:c r="N3" s="14" t="str">
+        <x:v>Trade impact is central: export competitiveness and shelf-life risk.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="14" t="str">
+        <x:v>AVDIS_003</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="str">
+        <x:v>AIRPORT_MIA</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>Miami / cargo aircraft operation</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F4" s="14" t="str">
+        <x:v>Cargo aircraft accident / investigation</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="str">
+        <x:v>Investigation</x:v>
+      </x:c>
+      <x:c r="H4" s="14" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="I4" s="14" t="str">
+        <x:v>Boeing 767 cargo aircraft runway overrun/crash killed five and injured five.</x:v>
+      </x:c>
+      <x:c r="J4" s="14" t="str">
+        <x:v>Potential local runway/airport cargo-flow disruption and operator safety scrutiny.</x:v>
+      </x:c>
+      <x:c r="K4" s="14" t="str">
+        <x:v>Accident-specific; no broad cargo tonnage estimate recorded.</x:v>
+      </x:c>
+      <x:c r="L4" s="14" t="str">
+        <x:v>SRC_SEC_012</x:v>
+      </x:c>
+      <x:c r="M4" s="14" t="str">
+        <x:v>https://aircargoweek.com/ntsb-issues-statement-on-miami-cargo-aircraft-crash/</x:v>
+      </x:c>
+      <x:c r="N4" s="14" t="str">
+        <x:v>Included as aviation-security/safety event from monitored source set.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>